--- a/08_Reports - Доклади - Berichte/Accounting_Cash_Flow/health_insurance_timeline.xlsx
+++ b/08_Reports - Доклади - Berichte/Accounting_Cash_Flow/health_insurance_timeline.xlsx
@@ -95,7 +95,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/10001_09-2024_Brutto_NettoProbe_00051_QZ1.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/10001_09-2024_Brutto_NettoProbe_00051_QZ1.pdf</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -142,7 +142,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/10001_09-2024_Brutto_NettoProbe_00107_QZ1.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/10001_09-2024_Brutto_NettoProbe_00107_QZ1.pdf</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -154,22 +154,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2021-02</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>TK</t>
+          <t>AOK Plus</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t/>
+          <t>1.02</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t/>
+          <t>25.01</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -189,34 +189,34 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/12-2024_Brutto_Netto_00090_X0B.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/02-2021 #9109.pdf</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2022-03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>TK</t>
+          <t>AOK Plus</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>991.96</t>
+          <t>-1890.88</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>833.58</t>
+          <t>25.02</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -236,7 +236,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/307538032.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/02-2022 #9109.pdf</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -248,7 +248,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2023-03</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -258,17 +258,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t/>
+          <t>-1316.88</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t/>
+          <t>28.02</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t/>
+          <t>1.23</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -283,39 +283,39 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/38389 - Vorgangsmappe Lohn - Contributions 28.05.2025.docx</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/02-2023 #9109.pdf</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2021-04</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Barmer</t>
+          <t>AOK Plus</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>4052.18</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1013.05</t>
+          <t>22.03</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1013.05</t>
+          <t/>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -330,34 +330,34 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/89878877, Antrag auf Ratenzahlung.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/04-2021 #9109.pdf</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t/>
+          <t>2022-05</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AOK</t>
+          <t>AOK Plus</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t/>
+          <t>1.05</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t/>
+          <t>4.05</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -377,19 +377,19 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Anforderung einer regelmäßigen Unbedenklichkeitsbescheinigung im Abonnement.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/04-2022 #9109.pdf</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2021-06</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -399,17 +399,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t/>
+          <t>-529.00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t/>
+          <t>1.06</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t/>
+          <t>-433.08</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -424,19 +424,19 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Antrag Freischaltung Mein AOK Arbeitgeberservice.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/06-2021 #9109.pdf</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2022-07</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -446,17 +446,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>88.53</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t/>
+          <t>4.07</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t/>
+          <t>-30.30</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -471,39 +471,39 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Aok plus.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/06-2022 #9109.pdf</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2021-07</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AOK</t>
+          <t>AOK Plus</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t/>
+          <t>11501.76</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t/>
+          <t>14.07</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t/>
+          <t>-433.08</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -518,39 +518,39 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Aok Sachsen Anhalt copy document from bank_.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/07-2021 #9109.pdf</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2022-08</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BKK</t>
+          <t>AOK Plus</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t/>
+          <t>1.09</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t/>
+          <t>31.08</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t/>
+          <t>19.08</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -565,34 +565,34 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/BKK Linde already clear . I paid.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/07-2022 #9109.pdf</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2021-08</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TK</t>
+          <t>AOK Plus</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>167412.67</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>167412.67</t>
+          <t>24.08</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -612,7 +612,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/BWA 03-2025.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/09-2021 #9109.pdf</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -624,7 +624,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -634,17 +634,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t/>
+          <t>-1238.29</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t/>
+          <t>21.10</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t/>
+          <t>30.09</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -659,19 +659,19 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Contributions 02.04.2025.docx</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/10-2022 #9109.pdf</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2021-08</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -681,17 +681,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t/>
+          <t>1.11</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>13649.05</t>
+          <t>26.10</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t/>
+          <t>-41.60</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -706,19 +706,19 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Contributions 03.03.2025.docx</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/11-2021 #9109.pdf</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2021-12</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -728,12 +728,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t/>
+          <t>-1296.34</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t/>
+          <t>15.12</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -753,19 +753,19 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Contributions 13.03.2025(1).docx</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/12-2021 #9109.pdf</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2022-12</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -775,17 +775,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t/>
+          <t>1.12</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t/>
+          <t>9.12</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t/>
+          <t>-23.43</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -800,24 +800,24 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Contributions 13.03.2025.docx</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/12-2022 #9109.pdf</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AOK Plus</t>
+          <t>TK</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>13649.05</t>
+          <t/>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -847,19 +847,19 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Contributions 19.02.2025.docx</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/12-2024_Brutto_Netto_00090_X0B.pdf</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t/>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>41544.44</t>
+          <t/>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>41544.44</t>
+          <t/>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -894,24 +894,24 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Contributions.docx</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/38389 - Vorgangsmappe Lohn - Contributions 28.05.2025.docx</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2004-12</t>
+          <t>2022-02</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DAK</t>
+          <t>AOK</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/DAK.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/aktuelle Unbedenklichkeitsbescheinigungen.pdf</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -953,12 +953,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t/>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>KKH</t>
+          <t>AOK</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Healts Vers..eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Anforderung einer regelmäßigen Unbedenklichkeitsbescheinigung im Abonnement.pdf</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1000,7 +1000,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>15451.27</t>
+          <t/>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1035,24 +1035,24 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Ihre Lohnauswertungen.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Antrag Freischaltung Mein AOK Arbeitgeberservice.pdf</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>KKH</t>
+          <t>AOK Plus</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/KKH(1).eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Contributions 02.04.2025.docx</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1094,12 +1094,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>KKH</t>
+          <t>AOK Plus</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t/>
+          <t>13649.05</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1129,24 +1129,24 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/KKH.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Contributions 03.03.2025.docx</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>KKH</t>
+          <t>AOK Plus</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/KKH1.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Contributions 13.03.2025(1).docx</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1188,7 +1188,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>41544.44</t>
+          <t/>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1223,24 +1223,24 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/original_msg(2).eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Contributions 13.03.2025.docx</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>AOK</t>
+          <t>AOK Plus</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t/>
+          <t>13649.05</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1270,19 +1270,19 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Petya Stefanova AOK.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Contributions 19.02.2025.docx</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t/>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1292,12 +1292,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>88.53</t>
+          <t>41544.44</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t/>
+          <t>41544.44</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Remaining health insurances for 09_2024 und 10_2024.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Contributions.docx</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1329,7 +1329,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1339,17 +1339,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>88.53</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>5.20</t>
+          <t/>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2494.00</t>
+          <t/>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1359,44 +1359,44 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>29.00</t>
+          <t/>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Tabelle nach § 175 InsO mit Grund des Bestreitens.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Remaining health insurances for 09_2024 und 10_2024.eml</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Barmer</t>
+          <t>AOK Plus</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t/>
+          <t>40.13</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t/>
+          <t>5.20</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t/>
+          <t>2494.00</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1406,34 +1406,34 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t/>
+          <t>29.00</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/UB.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Tabelle nach § 175 InsO mit Grund des Bestreitens.pdf</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>TK</t>
+          <t>Barmer</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2052.97</t>
+          <t/>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1458,34 +1458,34 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Vasilev_Test Pay Slip.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/UB.pdf</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2025-12</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>KKH</t>
+          <t>TK</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t/>
+          <t>2052.97</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2290.99</t>
+          <t/>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1505,34 +1505,34 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Zoll payment.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Vasilev_Test Pay Slip.pdf</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2022-02</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>DAK</t>
+          <t>TK</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t>8.03</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t/>
+          <t>17.02</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdgutschriftundrechnungen.zip::Rechnung 2014 vom 05.12.2024 Sendungsverlust Zahariev.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/02-2022 #9120.pdf</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1564,7 +1564,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2055-07</t>
+          <t>2022-04</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1574,12 +1574,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>12.11</t>
+          <t>9.05</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t/>
+          <t>17.03</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdperemailsendenmartinzaharievtransporte205407_0.zip::Martin Zahariev Transporte 2055 07.02.2025 Sendungsverluste.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/04-2022 #9120.pdf</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -1611,27 +1611,27 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2018-05</t>
+          <t>2022-06</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>TK</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t/>
+          <t>-24.90</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t/>
+          <t>-25.00</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t/>
+          <t>0.86</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1646,57 +1646,480 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/ihrelohnauswertungen3333.zip::BIG_Arbeitgeber_SEPA_Lastschriftmandat.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/06-2022 #9120.pdf</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>2022-08</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>TK</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>-74.00</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>-36.00</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/07-2022 #9120.pdf</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2022-10</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>TK</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>24.10</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>-25.41</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/10-2022 #9120.pdf</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2022-12</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>TK</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>12.12</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>18.11</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>-25.41</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/12-2022 #9120.pdf</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>2024-01</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>DAK</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>435.00</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>21.02</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/wgprqualifikationkepkdnr_60222rechnungjahresgeb.zip::20240123_60222_10160_Rechnung.pdf</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
+      <c r="E39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/20240123_60222_10160_Rechnung.pdf</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2018-05</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/BIG_Arbeitgeber_SEPA_Lastschriftmandat.pdf</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2024-02</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>TK</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>991.96</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>833.58</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/307538032.pdf</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>TK</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>167412.67</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>167412.67</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/BWA 03-2025.pdf</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>AOK Plus</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>15451.27</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Ihre Lohnauswertungen.eml</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2055-07</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>TK</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>12.11</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Transporte 2055 07.02.2025 Sendungsverluste.pdf</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>DAK</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>7.09</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Rechnung 2014 vom 05.12.2024 Sendungsverlust Zahariev.pdf</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>

--- a/08_Reports - Доклади - Berichte/Accounting_Cash_Flow/health_insurance_timeline.xlsx
+++ b/08_Reports - Доклади - Berichte/Accounting_Cash_Flow/health_insurance_timeline.xlsx
@@ -65,17 +65,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TK</t>
+          <t>AOK Plus</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t/>
+          <t>249.68</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t/>
+          <t>2496.77</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -95,34 +95,34 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/10001_09-2024_Brutto_NettoProbe_00051_QZ1.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/10001_01-2024_DivAuswertungen_DivMitarbeiter_2Z1 (2)-1.pdf</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>TK</t>
+          <t>AOK Plus</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>702400.72</t>
+          <t>941.48</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>516.00</t>
+          <t>2419.35</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -142,7 +142,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/10001_09-2024_Brutto_NettoProbe_00107_QZ1.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/10001_01-2024_DivAuswertungen_DivMitarbeiter_2Z1.pdf</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -154,7 +154,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2021-02</t>
+          <t>2024-07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -164,12 +164,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>682.88</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>25.01</t>
+          <t>7.03</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/02-2021 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/10001_02-2024_DivAuswertungen_00006_5Z1.pdf</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -201,7 +201,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2022-03</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -211,12 +211,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1890.88</t>
+          <t>2413.55</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>25.02</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -236,7 +236,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/02-2022 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/10001_03-2024_DivAuswertungen_DivMitarbeiter_8Z1.pdf</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -248,7 +248,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2023-03</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -258,17 +258,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1316.88</t>
+          <t>2413.55</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>28.02</t>
+          <t>12.04</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t/>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -283,7 +283,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/02-2023 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/10001_03-2024_DivAuswertungen_DivMitarbeiter_8Z1__copy2.pdf</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -295,7 +295,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2021-04</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -305,12 +305,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>366.67</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>22.03</t>
+          <t>1548.00</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -330,7 +330,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/04-2021 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/10001_04-2024_DivAuswertungen_DivMitarbeiter_BZ1.pdf</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -342,7 +342,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2022-05</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -352,12 +352,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>416.13</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>10.06</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -377,7 +377,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/04-2022 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/10001_05-2024_DivAuswertungen_DivMitarbeiter_EZ1.pdf</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -389,7 +389,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2021-06</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -399,17 +399,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-529.00</t>
+          <t>1118.00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1806.00</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-433.08</t>
+          <t/>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -424,7 +424,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/06-2021 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/10001_06-2024_DivAuswertungen_DivMitarbeiter_HZ1.pdf</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -436,7 +436,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2022-07</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -446,17 +446,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t/>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>946.00</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-30.30</t>
+          <t/>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -471,7 +471,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/06-2022 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/10001_06_2025_Div_Auswertungen_Div_Mitarbeiter.pdf</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -483,7 +483,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2021-07</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -493,17 +493,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>11501.76</t>
+          <t>1248.39</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>14.07</t>
+          <t>1914.19</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-433.08</t>
+          <t/>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -518,7 +518,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/07-2021 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/10001_07-2024_DivAuswertungen_DivMitarbeiter_KZ1.pdf</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -530,27 +530,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2022-08</t>
+          <t>2024-01</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AOK Plus</t>
+          <t>TK</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t/>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>31.08</t>
+          <t>1664.52</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t/>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/07-2022 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/10001_08-2024_Brutto_NettoProbe_00074_NZ1.pdf</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -577,22 +577,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2021-08</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AOK Plus</t>
+          <t>TK</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t/>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>24.08</t>
+          <t/>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -612,39 +612,39 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/09-2021 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/10001_08-2024_Brutto_NettoProbe_00098_NZ1.pdf</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2022-10</t>
+          <t>2024-01</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AOK Plus</t>
+          <t>TK</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-1238.29</t>
+          <t/>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>21.10</t>
+          <t/>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>30.09</t>
+          <t/>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -659,39 +659,39 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/10-2022 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/10001_09-2024_Brutto_NettoProbe_00051_QZ1.pdf</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2021-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>AOK Plus</t>
+          <t>TK</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>702400.72</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>26.10</t>
+          <t>516.00</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>-41.60</t>
+          <t/>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/11-2021 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/10001_09-2024_Brutto_NettoProbe_00107_QZ1.pdf</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -718,7 +718,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2021-12</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -728,12 +728,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-1296.34</t>
+          <t>2494.00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>15.12</t>
+          <t>2236.00</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/12-2021 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/10001_09-2024_DivAuswertungen_DivMitarbeiter_QZ1.pdf</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -765,27 +765,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2022-12</t>
+          <t>2023-12</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AOK Plus</t>
+          <t>TK</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t/>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>9.12</t>
+          <t>2619.35</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>-23.43</t>
+          <t/>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -800,7 +800,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/12-2022 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/10001_12-2023_Brutto_NettoProbe_00025_ZZ1.pdf</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -812,22 +812,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2023-11</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>TK</t>
+          <t>AOK Plus</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t/>
+          <t>2653.25</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t/>
+          <t>11.01</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -847,34 +847,34 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/12-2024_Brutto_Netto_00090_X0B.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/10001_12-2023_DivAuswertungen_DivMitarbeiter_ZZ1.pdf</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AOK Plus</t>
+          <t>BKK</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t/>
+          <t>2457.98</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t/>
+          <t>27.08</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -894,34 +894,34 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/38389 - Vorgangsmappe Lohn - Contributions 28.05.2025.docx</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/Health Security.pdf</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2022-02</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AOK</t>
+          <t>AOK Plus</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t/>
+          <t>2196.75</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t/>
+          <t>2494.00</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -941,34 +941,34 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/aktuelle Unbedenklichkeitsbescheinigungen.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/Lohnauswertungen_April_2025.pdf</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t/>
+          <t>2024-07</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>AOK</t>
+          <t>KKH</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t/>
+          <t>1.07</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t/>
+          <t>915.48</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -988,19 +988,19 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Anforderung einer regelmäßigen Unbedenklichkeitsbescheinigung im Abonnement.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/Lohnauswertungen_Juli_2024.pdf</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1010,12 +1010,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t/>
+          <t>0.00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t/>
+          <t>10.06</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1035,19 +1035,19 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Antrag Freischaltung Mein AOK Arbeitgeberservice.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/Lohnauswertungen_Juli_2025.pdf</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2000-01</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1057,12 +1057,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t/>
+          <t>29.07</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t/>
+          <t>1798.00</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t/>
+          <t>29.07.2025</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1082,24 +1082,24 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Contributions 02.04.2025.docx</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/Lohnauswertungen_Juli_2025__copy2.pdf</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>AOK Plus</t>
+          <t>TK</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>13649.05</t>
+          <t/>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1129,29 +1129,29 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Contributions 03.03.2025.docx</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/Lohnauswertungen_Juni_2025.pdf</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2024-06</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>AOK Plus</t>
+          <t>BKK</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t/>
+          <t>1.01</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1176,19 +1176,19 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Contributions 13.03.2025(1).docx</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/Lohnauswertungen_Mai_2024.pdf</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t/>
+          <t>0.00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1223,24 +1223,24 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Contributions 13.03.2025.docx</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/Lohnauswertungen_März_2025.pdf</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>AOK Plus</t>
+          <t>KKH</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>13649.05</t>
+          <t/>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1270,19 +1270,19 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Contributions 19.02.2025.docx</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/Lohnauswertungen_November_2024-1.pdf</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t/>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1292,12 +1292,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>41544.44</t>
+          <t>1241.94</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>41544.44</t>
+          <t>1165.16</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1317,19 +1317,19 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Contributions.docx</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/Lohnauswertungen_Oktober_2024.pdf</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2023-12</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1339,12 +1339,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>88.53</t>
+          <t>27.12</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t/>
+          <t>6239.86</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t/>
+          <t>27.12.2023</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1364,39 +1364,39 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Remaining health insurances for 09_2024 und 10_2024.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/Pay Roll 12.2023.pdf</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>AOK Plus</t>
+          <t>Hauptzollamt linked Krankenkasse claim</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>84.00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>5.20</t>
+          <t>27.08</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2494.00</t>
+          <t/>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1406,12 +1406,12 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>29.00</t>
+          <t/>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Tabelle nach § 175 InsO mit Grund des Bestreitens.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/Seizures.pdf</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1423,22 +1423,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Barmer</t>
+          <t>Hauptzollamt linked Krankenkasse claim</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t/>
+          <t>1215.78</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t/>
+          <t>11.02</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1458,34 +1458,34 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/UB.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/Zoll Kitanov.pdf</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2024-01</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>TK</t>
+          <t>AOK Plus</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2052.97</t>
+          <t>29.01</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t/>
+          <t>5889.13</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1495,7 +1495,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t/>
+          <t>29.01.2024</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Vasilev_Test Pay Slip.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 01-2024.pdf</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1517,22 +1517,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2022-02</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>TK</t>
+          <t>AOK Plus</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>29.01</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>17.02</t>
+          <t>5692.86</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t/>
+          <t>29.01.2025</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/02-2022 #9120.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 01-2025.pdf</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1564,22 +1564,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2022-04</t>
+          <t>2024-02</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>TK</t>
+          <t>AOK Plus</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>9.05</t>
+          <t>27.02</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>17.03</t>
+          <t>7277.62</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t/>
+          <t>27.02.2024</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/04-2022 #9120.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 02-2024.pdf</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -1611,32 +1611,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2022-06</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>TK</t>
+          <t>AOK Plus</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>-24.90</t>
+          <t>26.02</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>-25.00</t>
+          <t>4981.86</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t/>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t/>
+          <t>26.02.2025</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/06-2022 #9120.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 02-2025.pdf</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -1658,32 +1658,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2022-08</t>
+          <t>2024-03</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>TK</t>
+          <t>AOK Plus</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>26.03</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-74.00</t>
+          <t>6556.53</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>-36.00</t>
+          <t/>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t/>
+          <t>26.03.2024</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/07-2022 #9120.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 03-2024.pdf</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -1705,32 +1705,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2022-10</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>TK</t>
+          <t>AOK Plus</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>27.03</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>24.10</t>
+          <t>4789.23</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>-25.41</t>
+          <t/>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t/>
+          <t>27.03.2025</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/10-2022 #9120.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 03-2025.pdf</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -1752,32 +1752,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2022-12</t>
+          <t>2024-04</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>TK</t>
+          <t>AOK Plus</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>12.12</t>
+          <t>26.04</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>18.11</t>
+          <t>5689.02</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>-25.41</t>
+          <t/>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t/>
+          <t>26.04.2024</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/12-2022 #9120.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 04-2024.pdf</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -1799,22 +1799,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2003-01</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>DAK</t>
+          <t>AOK Plus</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>435.00</t>
+          <t>28.04</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>21.02</t>
+          <t>4518.02</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t/>
+          <t>28.04.2025</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/20240123_60222_10160_Rechnung.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 04-2025.pdf</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -1846,22 +1846,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2018-05</t>
+          <t>2024-05</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>AOK Plus</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t/>
+          <t>29.05</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t/>
+          <t>5869.18</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t/>
+          <t>29.05.2024</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1881,34 +1881,34 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/BIG_Arbeitgeber_SEPA_Lastschriftmandat.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 05-2024.pdf</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2001-03</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>TK</t>
+          <t>AOK Plus</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>991.96</t>
+          <t>27.05</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>833.58</t>
+          <t>4634.82</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t/>
+          <t>27.05.2025</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/307538032.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 05-2025.pdf</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -1940,22 +1940,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2024-06</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>TK</t>
+          <t>AOK Plus</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>167412.67</t>
+          <t>26.06</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>167412.67</t>
+          <t>5991.28</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t/>
+          <t>26.06.2024</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/BWA 03-2025.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 06-2024.pdf</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -1987,7 +1987,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2000-01</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1997,12 +1997,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t/>
+          <t>26.06</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>15451.27</t>
+          <t>2474.01</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2012,7 +2012,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t/>
+          <t>26.06.2025</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2022,34 +2022,34 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Ihre Lohnauswertungen.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 06-2025.pdf</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2055-07</t>
+          <t>2024-07</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>TK</t>
+          <t>AOK Plus</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>12.11</t>
+          <t>29.07</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t/>
+          <t>5515.16</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t/>
+          <t>29.07.2024</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Transporte 2055 07.02.2025 Sendungsverluste.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 07-2024.pdf</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2081,47 +2081,4559 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>AOK Plus</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>28.08</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>7002.40</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>28.08.2024</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 08-2024.pdf</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>AOK Plus</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>26.09</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>7304.67</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>26.09.2024</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 09-2024.pdf</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>AOK Plus</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>28.10</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>6364.90</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>28.10.2024</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 10-2024.pdf</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>AOK Plus</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>27.11</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>7150.71</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>27.11.2024</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 11-2024.pdf</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
           <t>2024-12</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>AOK Plus</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>23.12</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>5236.01</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>23.12.2024</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 12-2024.pdf</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2021-02</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>AOK Plus</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>25.01</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/02-2021 #9109.pdf</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2022-03</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>AOK Plus</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>-1890.88</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>25.02</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/02-2022 #9109.pdf</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2023-03</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>AOK Plus</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>-1316.88</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>28.02</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/02-2023 #9109.pdf</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2021-04</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>AOK Plus</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>1.04</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>22.03</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/04-2021 #9109.pdf</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2022-05</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>AOK Plus</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>4.05</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/04-2022 #9109.pdf</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2021-06</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>AOK Plus</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>-529.00</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>1.06</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>-433.08</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/06-2021 #9109.pdf</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2022-07</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>AOK Plus</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>1.07</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>-30.30</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/06-2022 #9109.pdf</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2021-07</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>AOK Plus</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>11501.76</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>14.07</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>-433.08</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/07-2021 #9109.pdf</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2022-08</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>AOK Plus</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>31.08</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>19.08</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/07-2022 #9109.pdf</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2021-08</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>AOK Plus</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>24.08</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/09-2021 #9109.pdf</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2022-10</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>AOK Plus</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>-1238.29</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>21.10</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>30.09</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/10-2022 #9109.pdf</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2021-08</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>AOK Plus</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>1.11</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>26.10</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>-41.60</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/11-2021 #9109.pdf</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2021-12</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>AOK Plus</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>-1296.34</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>15.12</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/12-2021 #9109.pdf</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2022-12</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>AOK Plus</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>1.12</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>9.12</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>-23.43</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/12-2022 #9109.pdf</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>TK</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/12-2024_Brutto_Netto_00090_X0B.pdf</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>AOK Plus</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/38389 - Vorgangsmappe Lohn - Contributions 28.05.2025.docx</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2024-05</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>AOK Plus</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>1.01</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/9. Nachweise zur Anmeldung der Mitarbeiter beim Sozialversicherungsträger.pdf</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2022-02</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>AOK</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/aktuelle Unbedenklichkeitsbescheinigungen.pdf</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>AOK</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Anforderung einer regelmäßigen Unbedenklichkeitsbescheinigung im Abonnement.pdf</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>AOK Plus</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Antrag Freischaltung Mein AOK Arbeitgeberservice.pdf</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>AOK Plus</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Contributions 02.04.2025.docx</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>AOK Plus</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>13649.05</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Contributions 03.03.2025.docx</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>AOK Plus</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Contributions 13.03.2025(1).docx</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>AOK Plus</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Contributions 13.03.2025.docx</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>AOK Plus</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>13649.05</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Contributions 19.02.2025.docx</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>AOK Plus</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>41544.44</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>41544.44</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Contributions.docx</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>AOK Plus</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>88.53</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Remaining health insurances for 09_2024 und 10_2024.eml</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>AOK</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/SEPA AOK Sachsen-Anhalt.pdf</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2020-06</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>AOK Plus</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>1.01</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>13.04</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Sozialversicherungsanmeldungen 01-2020 bis 03-2021.pdf</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2022-04</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>AOK</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>8.04</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Sozialversicherungsanmeldungen.pdf</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2020-06</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>AOK Plus</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>14.07</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/SV-Nachweis (DEЪV)_Div Mitarbeiter_   (07-2021.pdf</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2023-03</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>AOK Plus</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>1.01</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/SV-Nachweise.pdf</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>AOK Plus</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>40.13</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>5.20</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>2494.00</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>29.00</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Tabelle nach § 175 InsO mit Grund des Bestreitens.pdf</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Barmer</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/UB.pdf</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>TK</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>2052.97</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Vasilev_Test Pay Slip.pdf</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>KKH</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Lohnauswertungen_August_2024.pdf</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2024-07</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>AOK Plus</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>366.67</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>1548.00</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Test Pay ROll.pdf</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2022-02</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>TK</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>8.03</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>17.02</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/02-2022 #9120.pdf</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2022-04</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>TK</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>9.05</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>17.03</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/04-2022 #9120.pdf</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2022-06</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>TK</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>-24.90</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>-25.00</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>0.86</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/06-2022 #9120.pdf</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2022-08</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>TK</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>-74.00</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>-36.00</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/07-2022 #9120.pdf</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2022-10</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>TK</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>24.10</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>-25.41</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/10-2022 #9120.pdf</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2002-01</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>AOK Plus</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>29.03</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>16.01</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>-213.26</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>29.03.2023</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/10. Nachweis von Lohnzahlungen - Bankkontoumsätze 2023.pdf</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2002-01</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>AOK Plus</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>1.01</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>3.01</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>68848.69</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/10. Nachweis von Lohnzahlungen - Bankkontoumsätze 2024.pdf</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2022-12</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>TK</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>12.12</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>18.11</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>-25.41</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/12-2022 #9120.pdf</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2024-01</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
         <is>
           <t>DAK</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>435.00</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>21.02</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/20240123_60222_10160_Rechnung.pdf</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>AOK Plus</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>812.38</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>11.06</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform) (1).pdf</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2023-12</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Hauptzollamt linked Krankenkasse claim</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>56169.51</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>12.01</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform) (1)__copy10.pdf</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2024-05</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Hauptzollamt linked Krankenkasse claim</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>54426.97</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>12.06</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform) (1)__copy2.pdf</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Hauptzollamt linked Krankenkasse claim</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>52656.37</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>13.09</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform) (1)__copy4.pdf</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Hauptzollamt linked Krankenkasse claim</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>1250.78</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>15.01</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform) (2) (1).pdf</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>AOK</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>17870.97</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>10.10</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform) (2).pdf</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Hauptzollamt linked Krankenkasse claim</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>1222.78</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>10.12</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform) (2)__copy2.pdf</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2024-01</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Hauptzollamt linked Krankenkasse claim</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>56666.80</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>15.02</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform) (2)__copy3.pdf</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>AOK Plus</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>1111.98</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>15.01</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform) (3) (1).pdf</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2024-02</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Hauptzollamt linked Krankenkasse claim</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>57567.96</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>8.03</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform) (3).pdf</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>AOK Plus</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>1111.98</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>10.12</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform) (3)__copy2.pdf</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Hauptzollamt linked Krankenkasse claim</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>53690.09</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>12.04</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform) (4).pdf</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2024-06</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Hauptzollamt linked Krankenkasse claim</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>54751.98</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>12.07</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform).pdf</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2024-04</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Hauptzollamt linked Krankenkasse claim</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>51557.87</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>8.05</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform)__copy2.pdf</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2024-07</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Hauptzollamt linked Krankenkasse claim</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>47793.00</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>9.08</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform)__copy4.pdf</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2018-05</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/BIG_Arbeitgeber_SEPA_Lastschriftmandat.pdf</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>AOK Plus</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>1551.97</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>11.11</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/SEPA - Health insurances.pdf</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>AOK Plus</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>1568.99</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>11.11</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/SEPA - Pfändungen.pdf</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>AOK Plus</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>1094.96</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>10.03</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/SEPA List health security-1.pdf</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>AOK Plus</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>1094.96</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>9.04</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/SEPA List health security.pdf</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>AOK Plus</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>1077.94</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>11.02</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/SEPA List health securitys.pdf</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Hauptzollamt linked Krankenkasse claim</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>4654.34</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>10.03</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/SEPA List seizures.pdf</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Hauptzollamt linked Krankenkasse claim</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>4809.45</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>9.04</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/SEPA List seizures__copy2.pdf</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>BKK</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>2457.98</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>18.07</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/SEPA-List halth security.pdf</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>AOK Plus</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>1094.96</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>13.05</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/SEPA-List health security.pdf</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Hauptzollamt linked Krankenkasse claim</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>2352.89</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>18.07</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/SEPA-List seizure.pdf</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Hauptzollamt linked Krankenkasse claim</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>3752.34</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>13.05</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/SEPA-List Seizures.pdf</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Hauptzollamt linked Krankenkasse claim</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>2312.56</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>10.06</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/SEPA-List seizures__copy2.pdf</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2024-02</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>TK</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>991.96</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>833.58</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/307538032.pdf</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>TK</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>167412.67</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>167412.67</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/BWA 03-2025.pdf</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>AOK Plus</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>15451.27</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Ihre Lohnauswertungen.eml</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2055-07</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>TK</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>12.11</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Transporte 2055 07.02.2025 Sendungsverluste.pdf</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>DAK</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
         <is>
           <t>7.09</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
+      <c r="D128" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
         <is>
           <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Rechnung 2014 vom 05.12.2024 Sendungsverlust Zahariev.pdf</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2024-01</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>AOK</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/8. Lohnabrechnungen aller Mitarbeiter.zip::8. Lohnabrechnungen aller Mitarbeiter/Entgeltabrechnungen 01-2024.pdf</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2024-02</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>AOK Plus</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>838.33</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/8. Lohnabrechnungen aller Mitarbeiter.zip::8. Lohnabrechnungen aller Mitarbeiter/Entgeltabrechnungen 02-2024.pdf</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>AOK Plus</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/8. Lohnabrechnungen aller Mitarbeiter.zip::8. Lohnabrechnungen aller Mitarbeiter/Entgeltabrechnungen 03-2024.pdf</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2023-04</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>AOK</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/8. Lohnabrechnungen aller Mitarbeiter.zip::8. Lohnabrechnungen aller Mitarbeiter/Entgeltabrechnungen 04-2023.pdf</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2024-04</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>AOK Plus</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>1548.00</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/8. Lohnabrechnungen aller Mitarbeiter.zip::8. Lohnabrechnungen aller Mitarbeiter/Entgeltabrechnungen 04-2024.pdf</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2023-05</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>AOK</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/8. Lohnabrechnungen aller Mitarbeiter.zip::8. Lohnabrechnungen aller Mitarbeiter/Entgeltabrechnungen 05-2023.pdf</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2023-06</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>AOK</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/8. Lohnabrechnungen aller Mitarbeiter.zip::8. Lohnabrechnungen aller Mitarbeiter/Entgeltabrechnungen 06-2023.pdf</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2023-07</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>AOK</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/8. Lohnabrechnungen aller Mitarbeiter.zip::8. Lohnabrechnungen aller Mitarbeiter/Entgeltabrechnungen 07-2023.pdf</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2023-08</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>AOK</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/8. Lohnabrechnungen aller Mitarbeiter.zip::8. Lohnabrechnungen aller Mitarbeiter/Entgeltabrechnungen 08-2023.pdf</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2023-09</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>AOK</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/8. Lohnabrechnungen aller Mitarbeiter.zip::8. Lohnabrechnungen aller Mitarbeiter/Entgeltabrechnungen 09-2023.pdf</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2023-10</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>AOK</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/8. Lohnabrechnungen aller Mitarbeiter.zip::8. Lohnabrechnungen aller Mitarbeiter/Entgeltabrechnungen 10-2023.pdf</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2023-11</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>AOK</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/8. Lohnabrechnungen aller Mitarbeiter.zip::8. Lohnabrechnungen aller Mitarbeiter/Entgeltabrechnungen 11-2023.pdf</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2023-12</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>AOK</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/8. Lohnabrechnungen aller Mitarbeiter.zip::8. Lohnabrechnungen aller Mitarbeiter/Entgeltabrechnungen 12-2023.pdf</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
     </row>

--- a/08_Reports - Доклади - Berichte/Accounting_Cash_Flow/health_insurance_timeline.xlsx
+++ b/08_Reports - Доклади - Berichte/Accounting_Cash_Flow/health_insurance_timeline.xlsx
@@ -56,11 +56,26 @@
           <t>confidence</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>source_snippet</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>matched_pattern</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>extraction_method</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t/>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -70,7 +85,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>249.68</t>
+          <t/>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -101,13 +116,28 @@
       <c r="I2" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bezahlter Urlaub 2000 Gehalt L L J 2.496,77</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>bezahlt</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>health_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t/>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -117,7 +147,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>941.48</t>
+          <t/>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -148,13 +178,28 @@
       <c r="I3" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>bezahlter Urlaub 2000 Gehalt L L J 2.419,35</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>bezahlt</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>health_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t/>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -164,12 +209,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>682.88</t>
+          <t/>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>7.03</t>
+          <t/>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -194,14 +239,29 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>health_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t/>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -211,12 +271,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2413.55</t>
+          <t/>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t/>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -241,14 +301,29 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>health_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t/>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -258,12 +333,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2413.55</t>
+          <t/>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>12.04</t>
+          <t/>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -288,14 +363,29 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>health_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t/>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -305,7 +395,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>366.67</t>
+          <t/>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -336,13 +426,28 @@
       <c r="I7" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bezahlter Urlaub 2000 Gehalt L L J 1.548,00</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>bezahlt</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>health_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t/>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -352,12 +457,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>416.13</t>
+          <t/>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>10.06</t>
+          <t/>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -382,14 +487,29 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>health_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t/>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -399,7 +519,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1118.00</t>
+          <t/>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -430,13 +550,28 @@
       <c r="I9" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>bezahlter Urlaub 2000 Gehalt L L J 1.806,00</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>bezahlt</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>health_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2022-01</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -477,13 +612,28 @@
       <c r="I10" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>bezahlter Urlaub2000 Gehalt L L J 946,00</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>bezahlt</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>health_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t/>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -493,7 +643,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1248.39</t>
+          <t/>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -524,13 +674,28 @@
       <c r="I11" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bezahlter Urlaub 2000 Gehalt L L J 1.914,19</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>bezahlt</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>health_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t/>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -571,13 +736,28 @@
       <c r="I12" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bezahlter Urlaub 2000 Gehalt L L J 1.664,52</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>bezahlt</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>health_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t/>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -618,13 +798,28 @@
       <c r="I13" t="inlineStr">
         <is>
           <t>LOW</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>health_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t/>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -665,13 +860,28 @@
       <c r="I14" t="inlineStr">
         <is>
           <t>LOW</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>health_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t/>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -681,7 +891,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>702400.72</t>
+          <t/>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -712,13 +922,28 @@
       <c r="I15" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bezahlter Urlaub 2000 Gehalt L L J 516,00</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>bezahlt</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>health_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t/>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -728,7 +953,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2494.00</t>
+          <t/>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -759,13 +984,28 @@
       <c r="I16" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>bezahlter Urlaub 2000 Gehalt L L J 2.236,00</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>bezahlt</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>health_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2023-12</t>
+          <t/>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -806,13 +1046,28 @@
       <c r="I17" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>bezahlter Urlaub 2000 Gehalt L L J 2.619,35</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>bezahlt</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>health_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2023-11</t>
+          <t/>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -822,12 +1077,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2653.25</t>
+          <t/>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>11.01</t>
+          <t/>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -852,7 +1107,22 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>health_labeled_amounts</t>
         </is>
       </c>
     </row>
@@ -869,12 +1139,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2457.98</t>
+          <t/>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>27.08</t>
+          <t/>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -899,14 +1169,29 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>health_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t/>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -916,7 +1201,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2196.75</t>
+          <t/>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -947,6 +1232,21 @@
       <c r="I20" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>bezahlter Urlaub2000 Gehalt L L J 2.494,00</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>bezahlt</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>health_labeled_amounts</t>
         </is>
       </c>
     </row>
@@ -963,7 +1263,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t/>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -994,13 +1294,28 @@
       <c r="I21" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>bezahlter Urlaub 2000 Gehalt L L J 915,48</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>bezahlt</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>health_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1010,12 +1325,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t/>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>10.06</t>
+          <t/>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1040,14 +1355,29 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>health_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2000-01</t>
+          <t>2020-07</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1057,7 +1387,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>29.07</t>
+          <t>1798.00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1088,13 +1418,28 @@
       <c r="I23" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>beiträge bereits bezahlt wurden. ***Finanzamt 09097 Chemnitz Bar/Einzug 215/291/01497 07/2025 1.798,00</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Beiträge</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>health_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t/>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1135,6 +1480,21 @@
       <c r="I24" t="inlineStr">
         <is>
           <t>LOW</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>health_labeled_amounts</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1511,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t/>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1181,7 +1541,22 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>health_labeled_amounts</t>
         </is>
       </c>
     </row>
@@ -1198,7 +1573,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t/>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1228,19 +1603,34 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>health_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>KKH</t>
+          <t>AOK Plus</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1250,7 +1640,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t/>
+          <t>1165.16</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1270,19 +1660,34 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/Lohnauswertungen_November_2024-1.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/Lohnauswertungen_Oktober_2024.pdf</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>bezahlter Urlaub 2000 Gehalt L L J 1.165,16</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>bezahlt</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>health_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2023-12</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1292,12 +1697,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1241.94</t>
+          <t>6239.86</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1165.16</t>
+          <t>6239.86</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1307,7 +1712,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t/>
+          <t>27.12.2023</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1317,19 +1722,34 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/Lohnauswertungen_Oktober_2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/Pay Roll 12.2023.pdf</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>beiträge bereits bezahlt wurden. *** Finanzamt 09097 Chemnitz Bar/Einzug 215/291/01497 12/2023 6.239,86</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Beiträge</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>health_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2023-12</t>
+          <t>2021-02</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1339,12 +1759,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>27.12</t>
+          <t/>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>6239.86</t>
+          <t>-10000.00</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1354,7 +1774,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>27.12.2023</t>
+          <t/>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1364,34 +1784,49 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/Pay Roll 12.2023.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/02-2021 #9109.pdf</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Überweisung transfer -10.000,00</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Überweisung</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>health_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2022-02</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Hauptzollamt linked Krankenkasse claim</t>
+          <t>AOK Plus</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>84.00</t>
+          <t>-949.37</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>27.08</t>
+          <t>952.60</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1411,39 +1846,54 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/Seizures.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/02-2022 #9109.pdf</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Beitraege 02/22 -949,37</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Beitraege</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>health_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2023-02</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Hauptzollamt linked Krankenkasse claim</t>
+          <t>AOK Plus</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1215.78</t>
+          <t>-2190.52</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>11.02</t>
+          <t>-200.00</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t/>
+          <t>1.23</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1458,19 +1908,34 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/Zoll Kitanov.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/02-2023 #9109.pdf</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Beitraege 02/23 -2.190,52</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Beitraege</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>health_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2021-04</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1480,12 +1945,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>29.01</t>
+          <t/>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>5889.13</t>
+          <t>-775.00</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1495,7 +1960,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>29.01.2024</t>
+          <t/>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1505,19 +1970,34 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 01-2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/04-2021 #9109.pdf</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Überweisung Miete für 04/2021 -775,00</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Überweisung</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>health_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2022-04</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1527,12 +2007,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>29.01</t>
+          <t>-947.83</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>5692.86</t>
+          <t>-789.61</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1542,7 +2022,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>29.01.2025</t>
+          <t/>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1552,19 +2032,34 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 01-2025.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/04-2022 #9109.pdf</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Beitraege 04/22 -947,83</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Beitraege</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>health_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2021-06</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1574,22 +2069,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>27.02</t>
+          <t/>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>7277.62</t>
+          <t>-1400.00</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t/>
+          <t>-433.08</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>27.02.2024</t>
+          <t/>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1599,19 +2094,34 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 02-2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/06-2021 #9109.pdf</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Überweisung Darlehen 05/2021 -1.400,00</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Überweisung</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>health_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2022-06</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1621,22 +2131,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>26.02</t>
+          <t>-935.88</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>4981.86</t>
+          <t>-100.00</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t/>
+          <t>-30.30</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>26.02.2025</t>
+          <t/>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1646,19 +2156,34 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 02-2025.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/06-2022 #9109.pdf</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Beitraege 06/22 -935,88</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Beitraege</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>health_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2021-07</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1668,22 +2193,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>26.03</t>
+          <t/>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>6556.53</t>
+          <t>-1877.24</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t/>
+          <t>-433.08</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>26.03.2024</t>
+          <t/>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1693,19 +2218,34 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 03-2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/07-2021 #9109.pdf</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Überweisung Lohn-Gehalt Abrechnung 06/2021 -1.877,24</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Überweisung</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>health_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2022-07</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1715,22 +2255,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>27.03</t>
+          <t>-1030.32</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>4789.23</t>
+          <t>-2750.24</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t/>
+          <t>19.08</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>27.03.2025</t>
+          <t/>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1740,19 +2280,34 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 03-2025.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/07-2022 #9109.pdf</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Beitraege 08/22 -1.030,32</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Beitraege</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>health_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2021-09</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1762,12 +2317,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>26.04</t>
+          <t>-1701.61</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>5689.02</t>
+          <t>-500.00</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1777,7 +2332,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>26.04.2024</t>
+          <t/>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1787,19 +2342,34 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 04-2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/09-2021 #9109.pdf</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Beitraege 08/21 -1.701,61</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Beitraege</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>health_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2003-01</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1809,22 +2379,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>28.04</t>
+          <t>-983.10</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>4518.02</t>
+          <t>-600.00</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t/>
+          <t>30.09</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>28.04.2025</t>
+          <t/>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -1834,19 +2404,34 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 04-2025.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/10-2022 #9109.pdf</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Beitraege 10/22 -983,10</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Beitraege</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>health_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2021-11</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1856,22 +2441,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>29.05</t>
+          <t>-12.00</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>5869.18</t>
+          <t>-700.00</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t/>
+          <t>-41.60</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>29.05.2024</t>
+          <t/>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1881,19 +2466,34 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 05-2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/11-2021 #9109.pdf</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Beitraege1 0/21 -12,00</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Beitraege</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>health_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2001-03</t>
+          <t>2021-12</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1903,12 +2503,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>27.05</t>
+          <t>-923.29</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>4634.82</t>
+          <t>-1000.00</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1918,7 +2518,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>27.05.2025</t>
+          <t/>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -1928,19 +2528,34 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 05-2025.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/12-2021 #9109.pdf</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Beitraege 11/21 -923,29</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Beitraege</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>health_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2022-12</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1950,22 +2565,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>26.06</t>
+          <t>-1190.42</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>5991.28</t>
+          <t>-500.00</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t/>
+          <t>-23.43</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>26.06.2024</t>
+          <t/>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -1975,34 +2590,49 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 06-2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/12-2022 #9109.pdf</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Beitraege 11/22 -1.190,42</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Beitraege</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>health_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2000-01</t>
+          <t/>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>AOK Plus</t>
+          <t>TK</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>26.06</t>
+          <t/>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2474.01</t>
+          <t/>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2012,7 +2642,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>26.06.2025</t>
+          <t/>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2022,19 +2652,34 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 06-2025.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/12-2024_Brutto_Netto_00090_X0B.pdf</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>health_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2044,12 +2689,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>29.07</t>
+          <t/>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>5515.16</t>
+          <t/>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2059,7 +2704,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>29.07.2024</t>
+          <t/>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2069,19 +2714,34 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 07-2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/38389 - Vorgangsmappe Lohn - Contributions 28.05.2025.docx</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>health_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-05</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2091,12 +2751,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>28.08</t>
+          <t/>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>7002.40</t>
+          <t/>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2106,7 +2766,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>28.08.2024</t>
+          <t/>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2116,34 +2776,49 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 08-2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/9. Nachweise zur Anmeldung der Mitarbeiter beim Sozialversicherungsträger.pdf</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>health_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2022-02</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>AOK Plus</t>
+          <t>AOK</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>26.09</t>
+          <t/>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>7304.67</t>
+          <t/>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2153,7 +2828,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>26.09.2024</t>
+          <t/>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2163,34 +2838,49 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 09-2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/aktuelle Unbedenklichkeitsbescheinigungen.pdf</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>health_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t/>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>AOK Plus</t>
+          <t>AOK</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>28.10</t>
+          <t/>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>6364.90</t>
+          <t/>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2200,7 +2890,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>28.10.2024</t>
+          <t/>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2210,19 +2900,34 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 10-2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Anforderung einer regelmäßigen Unbedenklichkeitsbescheinigung im Abonnement.pdf</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>health_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t/>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2232,12 +2937,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>27.11</t>
+          <t/>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>7150.71</t>
+          <t/>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2247,7 +2952,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>27.11.2024</t>
+          <t/>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2257,19 +2962,34 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 11-2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Antrag Freischaltung Mein AOK Arbeitgeberservice.pdf</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>health_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2279,12 +2999,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>23.12</t>
+          <t/>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>5236.01</t>
+          <t/>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2294,7 +3014,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>23.12.2024</t>
+          <t/>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2304,19 +3024,34 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 12-2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Contributions 02.04.2025.docx</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>health_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2021-02</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2326,12 +3061,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t/>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>25.01</t>
+          <t/>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2351,19 +3086,34 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/02-2021 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Contributions 03.03.2025.docx</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>health_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2022-03</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2373,12 +3123,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>-1890.88</t>
+          <t/>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>25.02</t>
+          <t/>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2398,19 +3148,34 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/02-2022 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Contributions 13.03.2025(1).docx</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>health_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2023-03</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2420,17 +3185,17 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>-1316.88</t>
+          <t/>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>28.02</t>
+          <t/>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t/>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2445,19 +3210,34 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/02-2023 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Contributions 13.03.2025.docx</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>health_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2021-04</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2467,12 +3247,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t/>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>22.03</t>
+          <t/>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2492,19 +3272,34 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/04-2021 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Contributions 19.02.2025.docx</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>health_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2022-05</t>
+          <t/>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2514,12 +3309,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t/>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t/>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2539,19 +3334,34 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/04-2022 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Contributions.docx</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>health_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2021-06</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2561,17 +3371,17 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>-529.00</t>
+          <t/>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t/>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>-433.08</t>
+          <t/>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2586,39 +3396,54 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/06-2021 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Remaining health insurances for 09_2024 und 10_2024.eml</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>health_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2022-07</t>
+          <t/>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>AOK Plus</t>
+          <t>AOK</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t/>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t/>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>-30.30</t>
+          <t/>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2633,19 +3458,34 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/06-2022 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/SEPA AOK Sachsen-Anhalt.pdf</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>health_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2021-07</t>
+          <t>2020-01</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2655,17 +3495,17 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>11501.76</t>
+          <t/>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>14.07</t>
+          <t/>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>-433.08</t>
+          <t/>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2680,39 +3520,54 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/07-2021 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Sozialversicherungsanmeldungen 01-2020 bis 03-2021.pdf</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>health_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2022-08</t>
+          <t/>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>AOK Plus</t>
+          <t>AOK</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t/>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>31.08</t>
+          <t/>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t/>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2727,19 +3582,34 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/07-2022 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Sozialversicherungsanmeldungen.pdf</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>health_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2021-08</t>
+          <t>2021-07</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2749,12 +3619,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t/>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>24.08</t>
+          <t/>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2774,19 +3644,34 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/09-2021 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/SV-Nachweis (DEЪV)_Div Mitarbeiter_   (07-2021.pdf</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>health_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2022-10</t>
+          <t>2023-03</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2796,17 +3681,17 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>-1238.29</t>
+          <t/>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>21.10</t>
+          <t/>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>30.09</t>
+          <t/>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2821,19 +3706,34 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/10-2022 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/SV-Nachweise.pdf</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>health_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2021-08</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2843,17 +3743,17 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>30000.00</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>26.10</t>
+          <t>5.20</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>-41.60</t>
+          <t>2494.00</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2863,39 +3763,54 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t/>
+          <t>29.00</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/11-2021 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Tabelle nach § 175 InsO mit Grund des Bestreitens.pdf</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Beiträge EUR GESAMTFORDERUNG 30.000,00</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Beiträge</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>health_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2021-12</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>AOK Plus</t>
+          <t>Barmer</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>-1296.34</t>
+          <t/>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>15.12</t>
+          <t/>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2915,39 +3830,54 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/12-2021 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/UB.pdf</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>health_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2022-12</t>
+          <t/>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>AOK Plus</t>
+          <t>TK</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t/>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>9.12</t>
+          <t/>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>-23.43</t>
+          <t/>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2962,24 +3892,39 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/12-2022 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Vasilev_Test Pay Slip.pdf</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>health_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t/>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>TK</t>
+          <t>AOK Plus</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2989,7 +3934,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t/>
+          <t>1548.00</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3009,19 +3954,34 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/12-2024_Brutto_Netto_00090_X0B.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Test Pay ROll.pdf</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>bezahlter Urlaub 2000 Gehalt L L J 1.548,00</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>bezahlt</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>health_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2023-01</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3036,17 +3996,17 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t/>
+          <t>-67.93</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t/>
+          <t>1.05</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t/>
+          <t>29.03.2023</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -3056,12 +4016,27 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/38389 - Vorgangsmappe Lohn - Contributions 28.05.2025.docx</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/10. Nachweis von Lohnzahlungen - Bankkontoumsätze 2023.pdf</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Lastschrift aus Kartenzahlung; BIC: PBNKDEFFXXX; IBAN: DE98 3701 0050 0555 6515 06 -67,93</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Lastschrift</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>health_labeled_amounts</t>
         </is>
       </c>
     </row>
@@ -3078,17 +4053,17 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t/>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t/>
+          <t>-1764.63</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t/>
+          <t>68848.69</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3103,24 +4078,39 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/9. Nachweise zur Anmeldung der Mitarbeiter beim Sozialversicherungsträger.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/10. Nachweis von Lohnzahlungen - Bankkontoumsätze 2024.pdf</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Lastschrift mangels Konto deckung oder wegen fe hlende r / fehlerhaften Angaben. -1.764,63</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Lastschrift</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>health_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2022-02</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>AOK</t>
+          <t>AOK Plus</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3150,19 +4140,34 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/aktuelle Unbedenklichkeitsbescheinigungen.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform) (1).pdf</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
           <t>LOW</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>health_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t/>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3197,12 +4202,27 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Anforderung einer regelmäßigen Unbedenklichkeitsbescheinigung im Abonnement.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform) (2).pdf</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
           <t>LOW</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>health_labeled_amounts</t>
         </is>
       </c>
     </row>
@@ -3244,19 +4264,34 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Antrag Freischaltung Mein AOK Arbeitgeberservice.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform) (3) (1).pdf</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
           <t>LOW</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>health_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3291,24 +4326,39 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Contributions 02.04.2025.docx</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform) (3)__copy2.pdf</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
           <t>LOW</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>health_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t/>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>AOK Plus</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3318,7 +4368,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>13649.05</t>
+          <t/>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -3338,19 +4388,34 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Contributions 03.03.2025.docx</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/BIG_Arbeitgeber_SEPA_Lastschriftmandat.pdf</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>health_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3385,12 +4450,27 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Contributions 13.03.2025(1).docx</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/SEPA - Health insurances.pdf</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
           <t>LOW</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>health_labeled_amounts</t>
         </is>
       </c>
     </row>
@@ -3432,19 +4512,34 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Contributions 13.03.2025.docx</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/SEPA List health security-1.pdf</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
           <t>LOW</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>health_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3459,7 +4554,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>13649.05</t>
+          <t/>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -3479,19 +4574,34 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Contributions 19.02.2025.docx</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/SEPA List health security.pdf</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>health_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t/>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3501,12 +4611,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>41544.44</t>
+          <t/>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>41544.44</t>
+          <t/>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -3526,29 +4636,44 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Contributions.docx</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/SEPA List health securitys.pdf</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>health_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>AOK Plus</t>
+          <t>BKK</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>88.53</t>
+          <t/>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -3573,24 +4698,39 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Remaining health insurances for 09_2024 und 10_2024.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/SEPA-List halth security.pdf</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>health_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t/>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>AOK</t>
+          <t>AOK Plus</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3620,34 +4760,49 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/SEPA AOK Sachsen-Anhalt.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/SEPA-List health security.pdf</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
           <t>LOW</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>health_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2020-06</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>AOK Plus</t>
+          <t>TK</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>801.50</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>13.04</t>
+          <t/>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -3667,34 +4822,49 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Sozialversicherungsanmeldungen 01-2020 bis 03-2021.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/BWA 03-2025.pdf</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Beiträge 801,50</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Beiträge</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>health_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2022-04</t>
+          <t>2024-03</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>AOK</t>
+          <t>AOK Plus</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t/>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>8.04</t>
+          <t/>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -3714,19 +4884,34 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Sozialversicherungsanmeldungen.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/8. Lohnabrechnungen aller Mitarbeiter.zip::8. Lohnabrechnungen aller Mitarbeiter/Entgeltabrechnungen 02-2024.pdf</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>health_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2020-06</t>
+          <t>2024-04</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3736,12 +4921,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t/>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>14.07</t>
+          <t/>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -3761,19 +4946,34 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/SV-Nachweis (DEЪV)_Div Mitarbeiter_   (07-2021.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/8. Lohnabrechnungen aller Mitarbeiter.zip::8. Lohnabrechnungen aller Mitarbeiter/Entgeltabrechnungen 03-2024.pdf</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>health_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2023-03</t>
+          <t>2024-05</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3783,12 +4983,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t/>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t/>
+          <t>1548.00</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -3808,7 +5008,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/SV-Nachweise.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/8. Lohnabrechnungen aller Mitarbeiter.zip::8. Lohnabrechnungen aller Mitarbeiter/Entgeltabrechnungen 04-2024.pdf</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -3816,2824 +5016,19 @@
           <t>HIGH</t>
         </is>
       </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>AOK Plus</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>40.13</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>5.20</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>2494.00</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>29.00</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Tabelle nach § 175 InsO mit Grund des Bestreitens.pdf</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>2024-09</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Barmer</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/UB.pdf</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>2025-12</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>TK</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>2052.97</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Vasilev_Test Pay Slip.pdf</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>2024-09</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>KKH</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Lohnauswertungen_August_2024.pdf</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>2024-07</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>AOK Plus</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>366.67</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>1548.00</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Test Pay ROll.pdf</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>2022-02</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>TK</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>8.03</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>17.02</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/02-2022 #9120.pdf</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>2022-04</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>TK</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>9.05</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>17.03</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/04-2022 #9120.pdf</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>2022-06</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>TK</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>-24.90</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>-25.00</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>0.86</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/06-2022 #9120.pdf</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>2022-08</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>TK</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>1.09</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>-74.00</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>-36.00</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/07-2022 #9120.pdf</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>2022-10</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>TK</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>1.09</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>24.10</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>-25.41</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/10-2022 #9120.pdf</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>2002-01</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>AOK Plus</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>29.03</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>16.01</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>-213.26</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>29.03.2023</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/10. Nachweis von Lohnzahlungen - Bankkontoumsätze 2023.pdf</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>2002-01</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>AOK Plus</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>1.01</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>3.01</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>68848.69</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/10. Nachweis von Lohnzahlungen - Bankkontoumsätze 2024.pdf</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>2022-12</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>TK</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>12.12</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>18.11</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>-25.41</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/12-2022 #9120.pdf</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>2024-01</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>DAK</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>435.00</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>21.02</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/20240123_60222_10160_Rechnung.pdf</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>AOK Plus</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>812.38</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>11.06</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform) (1).pdf</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>2023-12</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Hauptzollamt linked Krankenkasse claim</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>56169.51</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>12.01</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform) (1)__copy10.pdf</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>2024-05</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Hauptzollamt linked Krankenkasse claim</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>54426.97</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>12.06</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform) (1)__copy2.pdf</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>2024-08</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Hauptzollamt linked Krankenkasse claim</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>52656.37</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>13.09</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform) (1)__copy4.pdf</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>2024-12</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Hauptzollamt linked Krankenkasse claim</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>1250.78</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>15.01</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform) (2) (1).pdf</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>2024-09</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>AOK</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>17870.97</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>10.10</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform) (2).pdf</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>2024-11</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Hauptzollamt linked Krankenkasse claim</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>1222.78</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>10.12</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform) (2)__copy2.pdf</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>2024-01</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Hauptzollamt linked Krankenkasse claim</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>56666.80</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>15.02</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform) (2)__copy3.pdf</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>AOK Plus</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>1111.98</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>15.01</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform) (3) (1).pdf</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>2024-02</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Hauptzollamt linked Krankenkasse claim</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>57567.96</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>8.03</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform) (3).pdf</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>2024-12</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>AOK Plus</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>1111.98</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>10.12</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform) (3)__copy2.pdf</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>2024-03</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Hauptzollamt linked Krankenkasse claim</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>53690.09</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>12.04</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform) (4).pdf</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>2024-06</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Hauptzollamt linked Krankenkasse claim</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>54751.98</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>12.07</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform).pdf</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>2024-04</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Hauptzollamt linked Krankenkasse claim</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>51557.87</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>8.05</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform)__copy2.pdf</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>2024-07</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Hauptzollamt linked Krankenkasse claim</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>47793.00</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>9.08</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform)__copy4.pdf</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>2018-05</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/BIG_Arbeitgeber_SEPA_Lastschriftmandat.pdf</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>2024-11</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>AOK Plus</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>1551.97</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>11.11</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/SEPA - Health insurances.pdf</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>2024-10</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>AOK Plus</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>1568.99</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>11.11</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/SEPA - Pfändungen.pdf</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>2025-03</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>AOK Plus</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>1094.96</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>10.03</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/SEPA List health security-1.pdf</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>2025-04</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>AOK Plus</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>1094.96</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>9.04</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/SEPA List health security.pdf</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>2025-02</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>AOK Plus</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>1077.94</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>11.02</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/SEPA List health securitys.pdf</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>2025-02</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Hauptzollamt linked Krankenkasse claim</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>4654.34</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>10.03</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/SEPA List seizures.pdf</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>2025-03</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Hauptzollamt linked Krankenkasse claim</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>4809.45</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>9.04</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/SEPA List seizures__copy2.pdf</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>2025-07</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>BKK</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>2457.98</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>18.07</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/SEPA-List halth security.pdf</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>2025-05</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>AOK Plus</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>1094.96</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>13.05</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/SEPA-List health security.pdf</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Hauptzollamt linked Krankenkasse claim</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>2352.89</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>18.07</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/SEPA-List seizure.pdf</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>2025-04</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>Hauptzollamt linked Krankenkasse claim</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>3752.34</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>13.05</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/SEPA-List Seizures.pdf</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>2025-05</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Hauptzollamt linked Krankenkasse claim</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>2312.56</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>10.06</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/SEPA-List seizures__copy2.pdf</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>2024-02</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>TK</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>991.96</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>833.58</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/307538032.pdf</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>2025-03</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>TK</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>167412.67</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>167412.67</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/BWA 03-2025.pdf</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>2024-09</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>AOK Plus</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>15451.27</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Ihre Lohnauswertungen.eml</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>2055-07</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>TK</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>12.11</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Transporte 2055 07.02.2025 Sendungsverluste.pdf</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>2024-12</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>DAK</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>7.09</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Rechnung 2014 vom 05.12.2024 Sendungsverlust Zahariev.pdf</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>2024-01</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>AOK</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/8. Lohnabrechnungen aller Mitarbeiter.zip::8. Lohnabrechnungen aller Mitarbeiter/Entgeltabrechnungen 01-2024.pdf</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>2024-02</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>AOK Plus</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>838.33</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/8. Lohnabrechnungen aller Mitarbeiter.zip::8. Lohnabrechnungen aller Mitarbeiter/Entgeltabrechnungen 02-2024.pdf</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>2024-03</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>AOK Plus</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/8. Lohnabrechnungen aller Mitarbeiter.zip::8. Lohnabrechnungen aller Mitarbeiter/Entgeltabrechnungen 03-2024.pdf</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>2023-04</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>AOK</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/8. Lohnabrechnungen aller Mitarbeiter.zip::8. Lohnabrechnungen aller Mitarbeiter/Entgeltabrechnungen 04-2023.pdf</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>2024-04</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>AOK Plus</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>1548.00</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/8. Lohnabrechnungen aller Mitarbeiter.zip::8. Lohnabrechnungen aller Mitarbeiter/Entgeltabrechnungen 04-2024.pdf</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>2023-05</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>AOK</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/8. Lohnabrechnungen aller Mitarbeiter.zip::8. Lohnabrechnungen aller Mitarbeiter/Entgeltabrechnungen 05-2023.pdf</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>2023-06</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>AOK</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/8. Lohnabrechnungen aller Mitarbeiter.zip::8. Lohnabrechnungen aller Mitarbeiter/Entgeltabrechnungen 06-2023.pdf</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>2023-07</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>AOK</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/8. Lohnabrechnungen aller Mitarbeiter.zip::8. Lohnabrechnungen aller Mitarbeiter/Entgeltabrechnungen 07-2023.pdf</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>2023-08</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>AOK</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/8. Lohnabrechnungen aller Mitarbeiter.zip::8. Lohnabrechnungen aller Mitarbeiter/Entgeltabrechnungen 08-2023.pdf</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>2023-09</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>AOK</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/8. Lohnabrechnungen aller Mitarbeiter.zip::8. Lohnabrechnungen aller Mitarbeiter/Entgeltabrechnungen 09-2023.pdf</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>2023-10</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>AOK</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/8. Lohnabrechnungen aller Mitarbeiter.zip::8. Lohnabrechnungen aller Mitarbeiter/Entgeltabrechnungen 10-2023.pdf</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>2023-11</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>AOK</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/8. Lohnabrechnungen aller Mitarbeiter.zip::8. Lohnabrechnungen aller Mitarbeiter/Entgeltabrechnungen 11-2023.pdf</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>2023-12</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>AOK</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/8. Lohnabrechnungen aller Mitarbeiter.zip::8. Lohnabrechnungen aller Mitarbeiter/Entgeltabrechnungen 12-2023.pdf</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>bezahlter Urlaub 2000 Gehalt L L J 1.548,00</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>bezahlt</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>health_labeled_amounts</t>
         </is>
       </c>
     </row>
